--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2015/ILLINOIS_2015.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2015/ILLINOIS_2015.xlsx
@@ -4020,7 +4020,7 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>General Simon Bolivar</t>
+          <t>Gral. Simon Bolivar</t>
         </is>
       </c>
       <c r="C204">
@@ -6918,7 +6918,7 @@
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C365">
@@ -7231,7 +7231,7 @@
         <v>74</v>
       </c>
       <c r="D382">
-        <v>0.0009627644349613593</v>
+        <v>0.0009627644349613592</v>
       </c>
     </row>
     <row r="383">
@@ -14467,7 +14467,7 @@
         <v>71</v>
       </c>
       <c r="D784">
-        <v>0.0009237334443548177</v>
+        <v>0.0009237334443548176</v>
       </c>
     </row>
     <row r="785">
@@ -15540,7 +15540,7 @@
       </c>
       <c r="B844" t="inlineStr">
         <is>
-          <t>General Zaragoza</t>
+          <t>Gral. Zaragoza</t>
         </is>
       </c>
       <c r="C844">
@@ -18096,7 +18096,7 @@
       </c>
       <c r="B986" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C986">
@@ -18114,7 +18114,7 @@
       </c>
       <c r="B987" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 26 -</t>
+          <t>San Juan Mixtepec -Dto. 26 -</t>
         </is>
       </c>
       <c r="C987">
@@ -19050,7 +19050,7 @@
       </c>
       <c r="B1039" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C1039">
@@ -19068,7 +19068,7 @@
       </c>
       <c r="B1040" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 26 -</t>
+          <t>San Pedro Mixtepec -Dto. 26 -</t>
         </is>
       </c>
       <c r="C1040">
@@ -30235,7 +30235,7 @@
         <v>71</v>
       </c>
       <c r="D1660">
-        <v>0.0009237334443548177</v>
+        <v>0.0009237334443548176</v>
       </c>
     </row>
     <row r="1661">
